--- a/Assets/Excel/Upgrades/Upgrades.xlsx
+++ b/Assets/Excel/Upgrades/Upgrades.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PS23B\Unity\VGATeamD\Assets\Excel\Upgrades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenji\Documents\TeamD\Assets\Excel\Upgrades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFC48B0-8DDA-45F0-BC6D-858C56D477D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94E661F-85B3-4165-B497-CC65380333BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B54D6C5-B809-4B09-8F2C-D3461C945E11}"/>
+    <workbookView xWindow="12828" yWindow="0" windowWidth="10308" windowHeight="12336" xr2:uid="{4B54D6C5-B809-4B09-8F2C-D3461C945E11}"/>
   </bookViews>
   <sheets>
     <sheet name="Entities" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="330">
   <si>
     <t>Key</t>
     <phoneticPr fontId="1"/>
@@ -373,6 +373,787 @@
   <si>
     <t>とんがり帽子</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>児童労働</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブラック工場</t>
+  </si>
+  <si>
+    <t>ラジウム原子炉</t>
+  </si>
+  <si>
+    <t>秩序の再構築</t>
+  </si>
+  <si>
+    <t>ディープベイクプロセス</t>
+  </si>
+  <si>
+    <t>サイボーグ労働者</t>
+  </si>
+  <si>
+    <t>1日78時間</t>
+  </si>
+  <si>
+    <t>機械学習</t>
+  </si>
+  <si>
+    <t>ブラウニーポイントシステム</t>
+  </si>
+  <si>
+    <t>「ボランティア」のインターン</t>
+  </si>
+  <si>
+    <t>行動のリフレーミング</t>
+  </si>
+  <si>
+    <t>無限エンジン</t>
+  </si>
+  <si>
+    <t>N次元の製造ライン</t>
+  </si>
+  <si>
+    <t>ユニバーサル・オートメーション</t>
+  </si>
+  <si>
+    <t>ハサミで切れないクレジットカード</t>
+  </si>
+  <si>
+    <t>耐酸金庫</t>
+  </si>
+  <si>
+    <t>チョコレートコイン</t>
+  </si>
+  <si>
+    <t>指数関数的金利</t>
+  </si>
+  <si>
+    <t>金融の禅</t>
+  </si>
+  <si>
+    <t>財布道</t>
+  </si>
+  <si>
+    <t>マネーの原理</t>
+  </si>
+  <si>
+    <t>食べられるお金</t>
+  </si>
+  <si>
+    <t>グランド・スーパーサイクル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金儲けの秘訣</t>
+  </si>
+  <si>
+    <t>利他的ループ</t>
+  </si>
+  <si>
+    <t>所得申告額の減少</t>
+  </si>
+  <si>
+    <t>クッキーポイント</t>
+  </si>
+  <si>
+    <t>あの巨大なショートケーキ</t>
+  </si>
+  <si>
+    <t>生贄</t>
+  </si>
+  <si>
+    <t>おいしい恩恵</t>
+  </si>
+  <si>
+    <t>太陽祭</t>
+  </si>
+  <si>
+    <t>増築されたパンテオン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>天界の偉大なるクッキー職人</t>
+  </si>
+  <si>
+    <t>創造神話</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神権政治</t>
+  </si>
+  <si>
+    <t>見たことねぇラップ祈祷</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詩篇の朗読</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神々の戦争</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奇抜なアイデア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>幽霊</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイナス神論</t>
+  </si>
+  <si>
+    <t>聖堂の罠</t>
+  </si>
+  <si>
+    <t>フサフサのあごひげ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いにしえの魔道書</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キッチンの呪い</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法学校</t>
+  </si>
+  <si>
+    <t>禁じられた調合</t>
+  </si>
+  <si>
+    <t>クッキー魔術</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ウサギのトリック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デラックスな特注杖</t>
+  </si>
+  <si>
+    <t>呪文を唱える蜂</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魔法使いの地下室</t>
+  </si>
+  <si>
+    <t>不動の呪文詠唱</t>
+  </si>
+  <si>
+    <t>電気</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポリモーフィズム</t>
+  </si>
+  <si>
+    <t>魔術的現実主義</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>＃貨物船</t>
+    <rPh sb="1" eb="4">
+      <t>カモツセン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Plain</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バニラ星雲</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワームホール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイレージ会員</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワープドライブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコレートモノリス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジェネレーションシップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダイソン球</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後のフロンティア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自動操縦</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇宙の果てのレストラン</t>
+  </si>
+  <si>
+    <t>共通言語</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トロイド宇宙</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最優先指令</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇宙前景放射</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30分以内にお届けできなければ全額返金いたします</t>
+  </si>
+  <si>
+    <t>＃錬金術師</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古代の石版</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イカれた麦百姓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魂と売る契約</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正気のダンス</t>
+  </si>
+  <si>
+    <t>「健全な」踊り</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブレーン移植</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終末に向けた代替案</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イライラする呪文</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現実世界</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異次元ゴミ投棄場</t>
+  </si>
+  <si>
+    <t>埋め込み式極小ポータル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>彼の降臨</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家庭内分裂</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポータルガン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>帰り道</t>
+  </si>
+  <si>
+    <t>＃タイムマシン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次元転移装置</t>
+  </si>
+  <si>
+    <t>タイムパラドックスリゾルバー</t>
+  </si>
+  <si>
+    <t>量子的難問</t>
+  </si>
+  <si>
+    <t>因果律強制者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過去と未来の比較</t>
+  </si>
+  <si>
+    <t>遠い未来の法律</t>
+  </si>
+  <si>
+    <t>グレートループ仮説</t>
+  </si>
+  <si>
+    <t>クッキートピアンの夢想</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第二の秒</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加の時計の針</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追憶</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分裂した秒</t>
+  </si>
+  <si>
+    <t>忍耐廃止</t>
+  </si>
+  <si>
+    <t>耐時間性の椅子カバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過ちを正しに</t>
+  </si>
+  <si>
+    <t>＃反物質コンデンサー</t>
+    <rPh sb="1" eb="4">
+      <t>ハンブッシツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シュガー粒子</t>
+  </si>
+  <si>
+    <t>弦理論</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大型マカロン衝突器</t>
+  </si>
+  <si>
+    <t>ビッグバンベイク</t>
+  </si>
+  <si>
+    <t>リバースサイクロトロン</t>
+  </si>
+  <si>
+    <t>ナノ宇宙学</t>
+  </si>
+  <si>
+    <t>パルス</t>
+  </si>
+  <si>
+    <t>他にも基本的な超微粒子があるだろう、多分</t>
+  </si>
+  <si>
+    <t>量子櫛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベーキングノーベル賞</t>
+  </si>
+  <si>
+    <t>確定分子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風味そのもの</t>
+  </si>
+  <si>
+    <t>おいしい引力</t>
+  </si>
+  <si>
+    <t>従業員の小型化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原子の砂糖漬け</t>
+  </si>
+  <si>
+    <t>＃プリズム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宝石磨き</t>
+  </si>
+  <si>
+    <t>超純粋宇宙光</t>
+  </si>
+  <si>
+    <t>夜光性</t>
+  </si>
+  <si>
+    <t>陰影反転</t>
+  </si>
+  <si>
+    <t>クリスタルの鏡</t>
+  </si>
+  <si>
+    <t>光速制限</t>
+  </si>
+  <si>
+    <t>オッカムのレーザー</t>
+  </si>
+  <si>
+    <t>ハイパーブラック塗料</t>
+  </si>
+  <si>
+    <t>実験ゴーグル、ただしオシャレカラー</t>
+  </si>
+  <si>
+    <t>光の調達方法</t>
+  </si>
+  <si>
+    <t>逆光理論</t>
+  </si>
+  <si>
+    <t>光の聖域</t>
+  </si>
+  <si>
+    <t>第９の色</t>
+  </si>
+  <si>
+    <t>チョコレートライト</t>
+  </si>
+  <si>
+    <t>穀物色の虹</t>
+  </si>
+  <si>
+    <t>＃チャンス‐メーカー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あなたのラッキークッキー</t>
+  </si>
+  <si>
+    <t>「全てが水の泡になる」魔法のコイン</t>
+  </si>
+  <si>
+    <t>抽選勝利チケット</t>
+  </si>
+  <si>
+    <t>四葉のクローバー畑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トリックに関する虎の巻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レプラコーンの村</t>
+  </si>
+  <si>
+    <t>不可能発生装置</t>
+  </si>
+  <si>
+    <t>反迷信学</t>
+  </si>
+  <si>
+    <t>ウサギの足</t>
+  </si>
+  <si>
+    <t>改定確率論</t>
+  </si>
+  <si>
+    <t>0 面サイコロ</t>
+  </si>
+  <si>
+    <t>ちょっとした決定論</t>
+  </si>
+  <si>
+    <t>いい流れ</t>
+  </si>
+  <si>
+    <t>ポジティブの最大化</t>
+  </si>
+  <si>
+    <t>ギャンブラーの誤謬の誤謬</t>
+  </si>
+  <si>
+    <t>＃自己無限生成エンジン</t>
+    <rPh sb="1" eb="3">
+      <t>ジコ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ムゲン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メタベーカリー</t>
+  </si>
+  <si>
+    <t>マンデルブラウンシュガー</t>
+  </si>
+  <si>
+    <t>フラクタルなまやかし</t>
+  </si>
+  <si>
+    <t>ネスト化された宇宙論</t>
+  </si>
+  <si>
+    <t>メンガースポンジケーキ</t>
+  </si>
+  <si>
+    <t>特にユーモアのある一頭の牛</t>
+  </si>
+  <si>
+    <t>チョコレートウロボロス</t>
+  </si>
+  <si>
+    <t>ネステッド</t>
+  </si>
+  <si>
+    <t>空間充填繊維</t>
+  </si>
+  <si>
+    <t>終わりのない散文の本</t>
+  </si>
+  <si>
+    <t>全ての集合の集合</t>
+  </si>
+  <si>
+    <t>今回のアップグレード</t>
+  </si>
+  <si>
+    <t>箱</t>
+  </si>
+  <si>
+    <t>マルチスケール・プロファイリング</t>
+  </si>
+  <si>
+    <t>同じであればあるほどに</t>
+  </si>
+  <si>
+    <t>＃Javascript console</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>猫でも分かるJavaScriptコンソール</t>
+  </si>
+  <si>
+    <t>64ビット配列</t>
+  </si>
+  <si>
+    <t>スタックオーバーフロー</t>
+  </si>
+  <si>
+    <t>エンタープライズコンパイラー</t>
+  </si>
+  <si>
+    <t>シンタックスシュガー</t>
+  </si>
+  <si>
+    <t>一杯のおいしいコーヒー</t>
+  </si>
+  <si>
+    <t>食べる直前にベーキング</t>
+  </si>
+  <si>
+    <t>クッキー++</t>
+  </si>
+  <si>
+    <t>ソフトウエアアップデート</t>
+  </si>
+  <si>
+    <t>Game.Loop</t>
+  </si>
+  <si>
+    <t>eval()</t>
+  </si>
+  <si>
+    <t>君の一番のファン</t>
+  </si>
+  <si>
+    <t>ハッカーの影</t>
+  </si>
+  <si>
+    <t>PHP捕獲用バット</t>
+  </si>
+  <si>
+    <t>シミュレーション用フェールセーフ</t>
+  </si>
+  <si>
+    <t>＃施設</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明白な宿命</t>
+  </si>
+  <si>
+    <t>要するに多次元的宇宙</t>
+  </si>
+  <si>
+    <t>万物の変換</t>
+  </si>
+  <si>
+    <t>マルチバース工作員</t>
+  </si>
+  <si>
+    <t>脱出計画</t>
+  </si>
+  <si>
+    <t>ゲームデザイン</t>
+  </si>
+  <si>
+    <t>宇宙</t>
+  </si>
+  <si>
+    <t>多元宇宙戦争</t>
+  </si>
+  <si>
+    <t>モバイルポート</t>
+  </si>
+  <si>
+    <t>カプセル化リアリティー</t>
+  </si>
+  <si>
+    <t>外部からのクリック</t>
+  </si>
+  <si>
+    <t>ユニバーサル・アイドリング</t>
+  </si>
+  <si>
+    <t>五番目の壁を破れ</t>
+  </si>
+  <si>
+    <t>反対な世界</t>
+  </si>
+  <si>
+    <t>ローマに通じる他の道</t>
+  </si>
+  <si>
+    <t>＃Cortex baker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ニューラル自我制限</t>
+  </si>
+  <si>
+    <t>従え</t>
+  </si>
+  <si>
+    <t>ひとつまみの非合理性</t>
+  </si>
+  <si>
+    <t>前方と後方の脳半球</t>
+  </si>
+  <si>
+    <t>ニューラルネットワーキング</t>
+  </si>
+  <si>
+    <t>宇宙的ブレインストーム</t>
+  </si>
+  <si>
+    <t>メガ・セラピー</t>
+  </si>
+  <si>
+    <t>シナプス用潤滑剤</t>
+  </si>
+  <si>
+    <t>サイコキネシス</t>
+  </si>
+  <si>
+    <t>脊椎</t>
+  </si>
+  <si>
+    <t>ニューラフォーミング</t>
+  </si>
+  <si>
+    <t>認識論的トリック</t>
+  </si>
+  <si>
+    <t>ありとあらゆる考え</t>
+  </si>
+  <si>
+    <t>夢見る土地</t>
+  </si>
+  <si>
+    <t>知的財産の窃盗</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>＃You</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クローンの大おけ</t>
+  </si>
+  <si>
+    <t>エネルギーたっぷりの栄養</t>
+  </si>
+  <si>
+    <t>スタントダブル</t>
+  </si>
+  <si>
+    <t>クローンリサイクルセンター</t>
+  </si>
+  <si>
+    <t>クローンの放し飼い</t>
+  </si>
+  <si>
+    <t>遺伝子調整</t>
+  </si>
+  <si>
+    <t>多様性の力</t>
+  </si>
+  <si>
+    <t>自分をいたわる</t>
+  </si>
+  <si>
+    <t>ソース管理</t>
+  </si>
+  <si>
+    <t>みんなの固い絆</t>
+  </si>
+  <si>
+    <t>安全強化パトロール</t>
+  </si>
+  <si>
+    <t>クローンの権利</t>
+  </si>
+  <si>
+    <t>大家族</t>
+  </si>
+  <si>
+    <t>身体微調整効率化計画</t>
+  </si>
+  <si>
+    <t>寝る前にクローンたちに物語を読み聞かせなきゃ</t>
   </si>
 </sst>
 </file>
@@ -450,7 +1231,68 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -760,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222065CF-7C40-4549-836B-B81F737954AC}">
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D304"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.69921875" customWidth="1"/>
@@ -1534,6 +2376,9 @@
       <c r="B67" t="s">
         <v>5</v>
       </c>
+      <c r="C67" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
@@ -1542,6 +2387,9 @@
       <c r="B68" t="s">
         <v>6</v>
       </c>
+      <c r="C68" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
@@ -1550,6 +2398,9 @@
       <c r="B69" t="s">
         <v>7</v>
       </c>
+      <c r="C69" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
@@ -1558,6 +2409,9 @@
       <c r="B70" t="s">
         <v>8</v>
       </c>
+      <c r="C70" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
@@ -1566,6 +2420,9 @@
       <c r="B71" t="s">
         <v>9</v>
       </c>
+      <c r="C71" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
@@ -1574,6 +2431,9 @@
       <c r="B72" t="s">
         <v>10</v>
       </c>
+      <c r="C72" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
@@ -1582,6 +2442,9 @@
       <c r="B73" t="s">
         <v>11</v>
       </c>
+      <c r="C73" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
@@ -1590,6 +2453,9 @@
       <c r="B74" t="s">
         <v>12</v>
       </c>
+      <c r="C74" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
@@ -1598,6 +2464,9 @@
       <c r="B75" t="s">
         <v>13</v>
       </c>
+      <c r="C75" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
@@ -1606,6 +2475,9 @@
       <c r="B76" t="s">
         <v>14</v>
       </c>
+      <c r="C76" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
@@ -1614,6 +2486,9 @@
       <c r="B77" t="s">
         <v>15</v>
       </c>
+      <c r="C77" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
@@ -1622,6 +2497,9 @@
       <c r="B78" t="s">
         <v>16</v>
       </c>
+      <c r="C78" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
@@ -1630,6 +2508,9 @@
       <c r="B79" t="s">
         <v>17</v>
       </c>
+      <c r="C79" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
@@ -1638,6 +2519,9 @@
       <c r="B80" t="s">
         <v>18</v>
       </c>
+      <c r="C80" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A81" s="3" t="s">
@@ -1664,6 +2548,9 @@
       <c r="B83" t="s">
         <v>5</v>
       </c>
+      <c r="C83" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
@@ -1672,6 +2559,9 @@
       <c r="B84" t="s">
         <v>6</v>
       </c>
+      <c r="C84" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
@@ -1680,6 +2570,9 @@
       <c r="B85" t="s">
         <v>7</v>
       </c>
+      <c r="C85" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
@@ -1688,6 +2581,9 @@
       <c r="B86" t="s">
         <v>8</v>
       </c>
+      <c r="C86" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
@@ -1696,6 +2592,9 @@
       <c r="B87" t="s">
         <v>9</v>
       </c>
+      <c r="C87" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
@@ -1704,6 +2603,9 @@
       <c r="B88" t="s">
         <v>10</v>
       </c>
+      <c r="C88" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
@@ -1712,6 +2614,9 @@
       <c r="B89" t="s">
         <v>11</v>
       </c>
+      <c r="C89" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
@@ -1720,6 +2625,9 @@
       <c r="B90" t="s">
         <v>12</v>
       </c>
+      <c r="C90" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
@@ -1728,6 +2636,9 @@
       <c r="B91" t="s">
         <v>13</v>
       </c>
+      <c r="C91" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
@@ -1736,6 +2647,9 @@
       <c r="B92" t="s">
         <v>14</v>
       </c>
+      <c r="C92" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
@@ -1744,6 +2658,9 @@
       <c r="B93" t="s">
         <v>15</v>
       </c>
+      <c r="C93" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
@@ -1752,6 +2669,9 @@
       <c r="B94" t="s">
         <v>16</v>
       </c>
+      <c r="C94" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
@@ -1760,6 +2680,9 @@
       <c r="B95" t="s">
         <v>17</v>
       </c>
+      <c r="C95" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
@@ -1768,6 +2691,9 @@
       <c r="B96" t="s">
         <v>18</v>
       </c>
+      <c r="C96" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A97" s="3" t="s">
@@ -1794,6 +2720,9 @@
       <c r="B99" t="s">
         <v>5</v>
       </c>
+      <c r="C99" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
@@ -1802,6 +2731,9 @@
       <c r="B100" t="s">
         <v>6</v>
       </c>
+      <c r="C100" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
@@ -1810,6 +2742,9 @@
       <c r="B101" t="s">
         <v>7</v>
       </c>
+      <c r="C101" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
@@ -1818,6 +2753,9 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
+      <c r="C102" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
@@ -1826,6 +2764,9 @@
       <c r="B103" t="s">
         <v>9</v>
       </c>
+      <c r="C103" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
@@ -1834,6 +2775,9 @@
       <c r="B104" t="s">
         <v>10</v>
       </c>
+      <c r="C104" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
@@ -1842,6 +2786,9 @@
       <c r="B105" t="s">
         <v>11</v>
       </c>
+      <c r="C105" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
@@ -1850,6 +2797,9 @@
       <c r="B106" t="s">
         <v>12</v>
       </c>
+      <c r="C106" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
@@ -1858,6 +2808,9 @@
       <c r="B107" t="s">
         <v>13</v>
       </c>
+      <c r="C107" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
@@ -1866,6 +2819,9 @@
       <c r="B108" t="s">
         <v>14</v>
       </c>
+      <c r="C108" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
@@ -1874,6 +2830,9 @@
       <c r="B109" t="s">
         <v>15</v>
       </c>
+      <c r="C109" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
@@ -1882,6 +2841,9 @@
       <c r="B110" t="s">
         <v>16</v>
       </c>
+      <c r="C110" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
@@ -1890,6 +2852,9 @@
       <c r="B111" t="s">
         <v>17</v>
       </c>
+      <c r="C111" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
@@ -1898,6 +2863,9 @@
       <c r="B112" t="s">
         <v>18</v>
       </c>
+      <c r="C112" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A113" s="3" t="s">
@@ -1924,6 +2892,9 @@
       <c r="B115" t="s">
         <v>5</v>
       </c>
+      <c r="C115" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
@@ -1932,6 +2903,9 @@
       <c r="B116" t="s">
         <v>6</v>
       </c>
+      <c r="C116" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
@@ -1940,6 +2914,9 @@
       <c r="B117" t="s">
         <v>7</v>
       </c>
+      <c r="C117" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
@@ -1948,6 +2925,9 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
+      <c r="C118" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
@@ -1956,6 +2936,9 @@
       <c r="B119" t="s">
         <v>9</v>
       </c>
+      <c r="C119" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
@@ -1964,6 +2947,9 @@
       <c r="B120" t="s">
         <v>10</v>
       </c>
+      <c r="C120" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
@@ -1972,6 +2958,9 @@
       <c r="B121" t="s">
         <v>11</v>
       </c>
+      <c r="C121" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
@@ -1980,6 +2969,9 @@
       <c r="B122" t="s">
         <v>12</v>
       </c>
+      <c r="C122" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
@@ -1988,6 +2980,9 @@
       <c r="B123" t="s">
         <v>13</v>
       </c>
+      <c r="C123" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
@@ -1996,6 +2991,9 @@
       <c r="B124" t="s">
         <v>14</v>
       </c>
+      <c r="C124" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
@@ -2004,6 +3002,9 @@
       <c r="B125" t="s">
         <v>15</v>
       </c>
+      <c r="C125" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
@@ -2012,6 +3013,9 @@
       <c r="B126" t="s">
         <v>16</v>
       </c>
+      <c r="C126" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
@@ -2020,6 +3024,9 @@
       <c r="B127" t="s">
         <v>17</v>
       </c>
+      <c r="C127" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
@@ -2027,6 +3034,1879 @@
       </c>
       <c r="B128" t="s">
         <v>18</v>
+      </c>
+      <c r="C128" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>95</v>
+      </c>
+      <c r="B130" t="s">
+        <v>154</v>
+      </c>
+      <c r="C130" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>95</v>
+      </c>
+      <c r="B131" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>95</v>
+      </c>
+      <c r="B132" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>95</v>
+      </c>
+      <c r="B133" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>95</v>
+      </c>
+      <c r="B134" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>95</v>
+      </c>
+      <c r="B135" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>95</v>
+      </c>
+      <c r="B136" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>95</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>95</v>
+      </c>
+      <c r="B138" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>95</v>
+      </c>
+      <c r="B139" t="s">
+        <v>13</v>
+      </c>
+      <c r="C139" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>95</v>
+      </c>
+      <c r="B140" t="s">
+        <v>14</v>
+      </c>
+      <c r="C140" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>95</v>
+      </c>
+      <c r="B141" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>95</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>95</v>
+      </c>
+      <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>95</v>
+      </c>
+      <c r="B144" t="s">
+        <v>18</v>
+      </c>
+      <c r="C144" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>95</v>
+      </c>
+      <c r="B146" t="s">
+        <v>154</v>
+      </c>
+      <c r="C146" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>95</v>
+      </c>
+      <c r="B147" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>95</v>
+      </c>
+      <c r="B148" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>95</v>
+      </c>
+      <c r="B149" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>95</v>
+      </c>
+      <c r="B150" t="s">
+        <v>8</v>
+      </c>
+      <c r="C150" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>95</v>
+      </c>
+      <c r="B151" t="s">
+        <v>9</v>
+      </c>
+      <c r="C151" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>95</v>
+      </c>
+      <c r="B152" t="s">
+        <v>10</v>
+      </c>
+      <c r="C152" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>95</v>
+      </c>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>95</v>
+      </c>
+      <c r="B154" t="s">
+        <v>12</v>
+      </c>
+      <c r="C154" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>95</v>
+      </c>
+      <c r="B155" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>95</v>
+      </c>
+      <c r="B156" t="s">
+        <v>14</v>
+      </c>
+      <c r="C156" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A157" t="s">
+        <v>95</v>
+      </c>
+      <c r="B157" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A158" t="s">
+        <v>95</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A159" t="s">
+        <v>95</v>
+      </c>
+      <c r="B159" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A160" t="s">
+        <v>95</v>
+      </c>
+      <c r="B160" t="s">
+        <v>18</v>
+      </c>
+      <c r="C160" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A161" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A162" t="s">
+        <v>95</v>
+      </c>
+      <c r="B162" t="s">
+        <v>154</v>
+      </c>
+      <c r="C162" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A163" t="s">
+        <v>95</v>
+      </c>
+      <c r="B163" t="s">
+        <v>5</v>
+      </c>
+      <c r="C163" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A164" t="s">
+        <v>95</v>
+      </c>
+      <c r="B164" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A165" t="s">
+        <v>95</v>
+      </c>
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A166" t="s">
+        <v>95</v>
+      </c>
+      <c r="B166" t="s">
+        <v>8</v>
+      </c>
+      <c r="C166" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A167" t="s">
+        <v>95</v>
+      </c>
+      <c r="B167" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A168" t="s">
+        <v>95</v>
+      </c>
+      <c r="B168" t="s">
+        <v>10</v>
+      </c>
+      <c r="C168" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A169" t="s">
+        <v>95</v>
+      </c>
+      <c r="B169" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A170" t="s">
+        <v>95</v>
+      </c>
+      <c r="B170" t="s">
+        <v>12</v>
+      </c>
+      <c r="C170" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A171" t="s">
+        <v>95</v>
+      </c>
+      <c r="B171" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A172" t="s">
+        <v>95</v>
+      </c>
+      <c r="B172" t="s">
+        <v>14</v>
+      </c>
+      <c r="C172" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A173" t="s">
+        <v>95</v>
+      </c>
+      <c r="B173" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A174" t="s">
+        <v>95</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A175" t="s">
+        <v>95</v>
+      </c>
+      <c r="B175" t="s">
+        <v>17</v>
+      </c>
+      <c r="C175" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A176" t="s">
+        <v>95</v>
+      </c>
+      <c r="B176" t="s">
+        <v>18</v>
+      </c>
+      <c r="C176" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A177" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A178" t="s">
+        <v>95</v>
+      </c>
+      <c r="B178" t="s">
+        <v>154</v>
+      </c>
+      <c r="C178" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A179" t="s">
+        <v>95</v>
+      </c>
+      <c r="B179" t="s">
+        <v>5</v>
+      </c>
+      <c r="C179" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A180" t="s">
+        <v>95</v>
+      </c>
+      <c r="B180" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A181" t="s">
+        <v>95</v>
+      </c>
+      <c r="B181" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A182" t="s">
+        <v>95</v>
+      </c>
+      <c r="B182" t="s">
+        <v>8</v>
+      </c>
+      <c r="C182" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A183" t="s">
+        <v>95</v>
+      </c>
+      <c r="B183" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A184" t="s">
+        <v>95</v>
+      </c>
+      <c r="B184" t="s">
+        <v>10</v>
+      </c>
+      <c r="C184" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A185" t="s">
+        <v>95</v>
+      </c>
+      <c r="B185" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A186" t="s">
+        <v>95</v>
+      </c>
+      <c r="B186" t="s">
+        <v>12</v>
+      </c>
+      <c r="C186" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A187" t="s">
+        <v>95</v>
+      </c>
+      <c r="B187" t="s">
+        <v>13</v>
+      </c>
+      <c r="C187" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A188" t="s">
+        <v>95</v>
+      </c>
+      <c r="B188" t="s">
+        <v>14</v>
+      </c>
+      <c r="C188" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A189" t="s">
+        <v>95</v>
+      </c>
+      <c r="B189" t="s">
+        <v>15</v>
+      </c>
+      <c r="C189" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A190" t="s">
+        <v>95</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A191" t="s">
+        <v>95</v>
+      </c>
+      <c r="B191" t="s">
+        <v>17</v>
+      </c>
+      <c r="C191" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A192" t="s">
+        <v>95</v>
+      </c>
+      <c r="B192" t="s">
+        <v>18</v>
+      </c>
+      <c r="C192" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A193" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A194" t="s">
+        <v>95</v>
+      </c>
+      <c r="B194" t="s">
+        <v>154</v>
+      </c>
+      <c r="C194" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A195" t="s">
+        <v>95</v>
+      </c>
+      <c r="B195" t="s">
+        <v>5</v>
+      </c>
+      <c r="C195" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A196" t="s">
+        <v>95</v>
+      </c>
+      <c r="B196" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A197" t="s">
+        <v>95</v>
+      </c>
+      <c r="B197" t="s">
+        <v>7</v>
+      </c>
+      <c r="C197" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A198" t="s">
+        <v>95</v>
+      </c>
+      <c r="B198" t="s">
+        <v>8</v>
+      </c>
+      <c r="C198" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A199" t="s">
+        <v>95</v>
+      </c>
+      <c r="B199" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A200" t="s">
+        <v>95</v>
+      </c>
+      <c r="B200" t="s">
+        <v>10</v>
+      </c>
+      <c r="C200" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A201" t="s">
+        <v>95</v>
+      </c>
+      <c r="B201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A202" t="s">
+        <v>95</v>
+      </c>
+      <c r="B202" t="s">
+        <v>12</v>
+      </c>
+      <c r="C202" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A203" t="s">
+        <v>95</v>
+      </c>
+      <c r="B203" t="s">
+        <v>13</v>
+      </c>
+      <c r="C203" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A204" t="s">
+        <v>95</v>
+      </c>
+      <c r="B204" t="s">
+        <v>14</v>
+      </c>
+      <c r="C204" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A205" t="s">
+        <v>95</v>
+      </c>
+      <c r="B205" t="s">
+        <v>15</v>
+      </c>
+      <c r="C205" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A206" t="s">
+        <v>95</v>
+      </c>
+      <c r="B206" t="s">
+        <v>16</v>
+      </c>
+      <c r="C206" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A207" t="s">
+        <v>95</v>
+      </c>
+      <c r="B207" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A208" t="s">
+        <v>95</v>
+      </c>
+      <c r="B208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C208" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A209" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A210" t="s">
+        <v>95</v>
+      </c>
+      <c r="B210" t="s">
+        <v>154</v>
+      </c>
+      <c r="C210" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A211" t="s">
+        <v>95</v>
+      </c>
+      <c r="B211" t="s">
+        <v>5</v>
+      </c>
+      <c r="C211" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A212" t="s">
+        <v>95</v>
+      </c>
+      <c r="B212" t="s">
+        <v>6</v>
+      </c>
+      <c r="C212" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A213" t="s">
+        <v>95</v>
+      </c>
+      <c r="B213" t="s">
+        <v>7</v>
+      </c>
+      <c r="C213" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A214" t="s">
+        <v>95</v>
+      </c>
+      <c r="B214" t="s">
+        <v>8</v>
+      </c>
+      <c r="C214" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A215" t="s">
+        <v>95</v>
+      </c>
+      <c r="B215" t="s">
+        <v>9</v>
+      </c>
+      <c r="C215" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A216" t="s">
+        <v>95</v>
+      </c>
+      <c r="B216" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A217" t="s">
+        <v>95</v>
+      </c>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A218" t="s">
+        <v>95</v>
+      </c>
+      <c r="B218" t="s">
+        <v>12</v>
+      </c>
+      <c r="C218" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A219" t="s">
+        <v>95</v>
+      </c>
+      <c r="B219" t="s">
+        <v>13</v>
+      </c>
+      <c r="C219" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A220" t="s">
+        <v>95</v>
+      </c>
+      <c r="B220" t="s">
+        <v>14</v>
+      </c>
+      <c r="C220" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A221" t="s">
+        <v>95</v>
+      </c>
+      <c r="B221" t="s">
+        <v>15</v>
+      </c>
+      <c r="C221" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A222" t="s">
+        <v>95</v>
+      </c>
+      <c r="B222" t="s">
+        <v>16</v>
+      </c>
+      <c r="C222" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A223" t="s">
+        <v>95</v>
+      </c>
+      <c r="B223" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A224" t="s">
+        <v>95</v>
+      </c>
+      <c r="B224" t="s">
+        <v>18</v>
+      </c>
+      <c r="C224" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A225" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A226" t="s">
+        <v>95</v>
+      </c>
+      <c r="B226" t="s">
+        <v>154</v>
+      </c>
+      <c r="C226" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A227" t="s">
+        <v>95</v>
+      </c>
+      <c r="B227" t="s">
+        <v>5</v>
+      </c>
+      <c r="C227" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A228" t="s">
+        <v>95</v>
+      </c>
+      <c r="B228" t="s">
+        <v>6</v>
+      </c>
+      <c r="C228" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A229" t="s">
+        <v>95</v>
+      </c>
+      <c r="B229" t="s">
+        <v>7</v>
+      </c>
+      <c r="C229" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A230" t="s">
+        <v>95</v>
+      </c>
+      <c r="B230" t="s">
+        <v>8</v>
+      </c>
+      <c r="C230" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A231" t="s">
+        <v>95</v>
+      </c>
+      <c r="B231" t="s">
+        <v>9</v>
+      </c>
+      <c r="C231" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A232" t="s">
+        <v>95</v>
+      </c>
+      <c r="B232" t="s">
+        <v>10</v>
+      </c>
+      <c r="C232" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A233" t="s">
+        <v>95</v>
+      </c>
+      <c r="B233" t="s">
+        <v>11</v>
+      </c>
+      <c r="C233" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A234" t="s">
+        <v>95</v>
+      </c>
+      <c r="B234" t="s">
+        <v>12</v>
+      </c>
+      <c r="C234" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A235" t="s">
+        <v>95</v>
+      </c>
+      <c r="B235" t="s">
+        <v>13</v>
+      </c>
+      <c r="C235" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A236" t="s">
+        <v>95</v>
+      </c>
+      <c r="B236" t="s">
+        <v>14</v>
+      </c>
+      <c r="C236" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A237" t="s">
+        <v>95</v>
+      </c>
+      <c r="B237" t="s">
+        <v>15</v>
+      </c>
+      <c r="C237" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A238" t="s">
+        <v>95</v>
+      </c>
+      <c r="B238" t="s">
+        <v>16</v>
+      </c>
+      <c r="C238" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A239" t="s">
+        <v>95</v>
+      </c>
+      <c r="B239" t="s">
+        <v>17</v>
+      </c>
+      <c r="C239" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A240" t="s">
+        <v>95</v>
+      </c>
+      <c r="B240" t="s">
+        <v>18</v>
+      </c>
+      <c r="C240" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A241" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A242" t="s">
+        <v>95</v>
+      </c>
+      <c r="B242" t="s">
+        <v>154</v>
+      </c>
+      <c r="C242" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A243" t="s">
+        <v>95</v>
+      </c>
+      <c r="B243" t="s">
+        <v>5</v>
+      </c>
+      <c r="C243" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A244" t="s">
+        <v>95</v>
+      </c>
+      <c r="B244" t="s">
+        <v>6</v>
+      </c>
+      <c r="C244" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A245" t="s">
+        <v>95</v>
+      </c>
+      <c r="B245" t="s">
+        <v>7</v>
+      </c>
+      <c r="C245" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A246" t="s">
+        <v>95</v>
+      </c>
+      <c r="B246" t="s">
+        <v>8</v>
+      </c>
+      <c r="C246" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A247" t="s">
+        <v>95</v>
+      </c>
+      <c r="B247" t="s">
+        <v>9</v>
+      </c>
+      <c r="C247" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A248" t="s">
+        <v>95</v>
+      </c>
+      <c r="B248" t="s">
+        <v>10</v>
+      </c>
+      <c r="C248" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A249" t="s">
+        <v>95</v>
+      </c>
+      <c r="B249" t="s">
+        <v>11</v>
+      </c>
+      <c r="C249" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A250" t="s">
+        <v>95</v>
+      </c>
+      <c r="B250" t="s">
+        <v>12</v>
+      </c>
+      <c r="C250" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A251" t="s">
+        <v>95</v>
+      </c>
+      <c r="B251" t="s">
+        <v>13</v>
+      </c>
+      <c r="C251" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A252" t="s">
+        <v>95</v>
+      </c>
+      <c r="B252" t="s">
+        <v>14</v>
+      </c>
+      <c r="C252" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A253" t="s">
+        <v>95</v>
+      </c>
+      <c r="B253" t="s">
+        <v>15</v>
+      </c>
+      <c r="C253" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A254" t="s">
+        <v>95</v>
+      </c>
+      <c r="B254" t="s">
+        <v>16</v>
+      </c>
+      <c r="C254" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A255" t="s">
+        <v>95</v>
+      </c>
+      <c r="B255" t="s">
+        <v>17</v>
+      </c>
+      <c r="C255" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A256" t="s">
+        <v>95</v>
+      </c>
+      <c r="B256" t="s">
+        <v>18</v>
+      </c>
+      <c r="C256" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A257" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A258" t="s">
+        <v>95</v>
+      </c>
+      <c r="B258" t="s">
+        <v>154</v>
+      </c>
+      <c r="C258" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A259" t="s">
+        <v>95</v>
+      </c>
+      <c r="B259" t="s">
+        <v>5</v>
+      </c>
+      <c r="C259" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A260" t="s">
+        <v>95</v>
+      </c>
+      <c r="B260" t="s">
+        <v>6</v>
+      </c>
+      <c r="C260" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A261" t="s">
+        <v>95</v>
+      </c>
+      <c r="B261" t="s">
+        <v>7</v>
+      </c>
+      <c r="C261" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A262" t="s">
+        <v>95</v>
+      </c>
+      <c r="B262" t="s">
+        <v>8</v>
+      </c>
+      <c r="C262" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A263" t="s">
+        <v>95</v>
+      </c>
+      <c r="B263" t="s">
+        <v>9</v>
+      </c>
+      <c r="C263" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A264" t="s">
+        <v>95</v>
+      </c>
+      <c r="B264" t="s">
+        <v>10</v>
+      </c>
+      <c r="C264" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A265" t="s">
+        <v>95</v>
+      </c>
+      <c r="B265" t="s">
+        <v>11</v>
+      </c>
+      <c r="C265" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A266" t="s">
+        <v>95</v>
+      </c>
+      <c r="B266" t="s">
+        <v>12</v>
+      </c>
+      <c r="C266" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A267" t="s">
+        <v>95</v>
+      </c>
+      <c r="B267" t="s">
+        <v>13</v>
+      </c>
+      <c r="C267" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A268" t="s">
+        <v>95</v>
+      </c>
+      <c r="B268" t="s">
+        <v>14</v>
+      </c>
+      <c r="C268" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A269" t="s">
+        <v>95</v>
+      </c>
+      <c r="B269" t="s">
+        <v>15</v>
+      </c>
+      <c r="C269" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A270" t="s">
+        <v>95</v>
+      </c>
+      <c r="B270" t="s">
+        <v>16</v>
+      </c>
+      <c r="C270" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A271" t="s">
+        <v>95</v>
+      </c>
+      <c r="B271" t="s">
+        <v>17</v>
+      </c>
+      <c r="C271" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A272" t="s">
+        <v>95</v>
+      </c>
+      <c r="B272" t="s">
+        <v>18</v>
+      </c>
+      <c r="C272" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A273" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A274" t="s">
+        <v>95</v>
+      </c>
+      <c r="B274" t="s">
+        <v>154</v>
+      </c>
+      <c r="C274" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A275" t="s">
+        <v>95</v>
+      </c>
+      <c r="B275" t="s">
+        <v>5</v>
+      </c>
+      <c r="C275" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A276" t="s">
+        <v>95</v>
+      </c>
+      <c r="B276" t="s">
+        <v>6</v>
+      </c>
+      <c r="C276" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A277" t="s">
+        <v>95</v>
+      </c>
+      <c r="B277" t="s">
+        <v>7</v>
+      </c>
+      <c r="C277" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A278" t="s">
+        <v>95</v>
+      </c>
+      <c r="B278" t="s">
+        <v>8</v>
+      </c>
+      <c r="C278" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A279" t="s">
+        <v>95</v>
+      </c>
+      <c r="B279" t="s">
+        <v>9</v>
+      </c>
+      <c r="C279" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A280" t="s">
+        <v>95</v>
+      </c>
+      <c r="B280" t="s">
+        <v>10</v>
+      </c>
+      <c r="C280" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A281" t="s">
+        <v>95</v>
+      </c>
+      <c r="B281" t="s">
+        <v>11</v>
+      </c>
+      <c r="C281" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A282" t="s">
+        <v>95</v>
+      </c>
+      <c r="B282" t="s">
+        <v>12</v>
+      </c>
+      <c r="C282" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A283" t="s">
+        <v>95</v>
+      </c>
+      <c r="B283" t="s">
+        <v>13</v>
+      </c>
+      <c r="C283" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A284" t="s">
+        <v>95</v>
+      </c>
+      <c r="B284" t="s">
+        <v>14</v>
+      </c>
+      <c r="C284" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A285" t="s">
+        <v>95</v>
+      </c>
+      <c r="B285" t="s">
+        <v>15</v>
+      </c>
+      <c r="C285" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A286" t="s">
+        <v>95</v>
+      </c>
+      <c r="B286" t="s">
+        <v>16</v>
+      </c>
+      <c r="C286" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A287" t="s">
+        <v>95</v>
+      </c>
+      <c r="B287" t="s">
+        <v>17</v>
+      </c>
+      <c r="C287" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A288" t="s">
+        <v>95</v>
+      </c>
+      <c r="B288" t="s">
+        <v>18</v>
+      </c>
+      <c r="C288" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A289" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A290" t="s">
+        <v>95</v>
+      </c>
+      <c r="B290" t="s">
+        <v>154</v>
+      </c>
+      <c r="C290" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A291" t="s">
+        <v>95</v>
+      </c>
+      <c r="B291" t="s">
+        <v>5</v>
+      </c>
+      <c r="C291" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A292" t="s">
+        <v>95</v>
+      </c>
+      <c r="B292" t="s">
+        <v>6</v>
+      </c>
+      <c r="C292" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A293" t="s">
+        <v>95</v>
+      </c>
+      <c r="B293" t="s">
+        <v>7</v>
+      </c>
+      <c r="C293" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A294" t="s">
+        <v>95</v>
+      </c>
+      <c r="B294" t="s">
+        <v>8</v>
+      </c>
+      <c r="C294" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A295" t="s">
+        <v>95</v>
+      </c>
+      <c r="B295" t="s">
+        <v>9</v>
+      </c>
+      <c r="C295" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A296" t="s">
+        <v>95</v>
+      </c>
+      <c r="B296" t="s">
+        <v>10</v>
+      </c>
+      <c r="C296" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A297" t="s">
+        <v>95</v>
+      </c>
+      <c r="B297" t="s">
+        <v>11</v>
+      </c>
+      <c r="C297" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A298" t="s">
+        <v>95</v>
+      </c>
+      <c r="B298" t="s">
+        <v>12</v>
+      </c>
+      <c r="C298" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A299" t="s">
+        <v>95</v>
+      </c>
+      <c r="B299" t="s">
+        <v>13</v>
+      </c>
+      <c r="C299" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A300" t="s">
+        <v>95</v>
+      </c>
+      <c r="B300" t="s">
+        <v>14</v>
+      </c>
+      <c r="C300" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A301" t="s">
+        <v>95</v>
+      </c>
+      <c r="B301" t="s">
+        <v>15</v>
+      </c>
+      <c r="C301" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A302" t="s">
+        <v>95</v>
+      </c>
+      <c r="B302" t="s">
+        <v>16</v>
+      </c>
+      <c r="C302" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A303" t="s">
+        <v>95</v>
+      </c>
+      <c r="B303" t="s">
+        <v>17</v>
+      </c>
+      <c r="C303" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A304" t="s">
+        <v>95</v>
+      </c>
+      <c r="B304" t="s">
+        <v>18</v>
+      </c>
+      <c r="C304" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/Upgrades/Upgrades.xlsx
+++ b/Assets/Excel/Upgrades/Upgrades.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenji\Documents\TeamD\Assets\Excel\Upgrades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PS23B\Unity\VGATeamD\Assets\Excel\Upgrades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94E661F-85B3-4165-B497-CC65380333BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8040BF4D-4003-4F9F-B0C4-BDEA5FA60EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12828" yWindow="0" windowWidth="10308" windowHeight="12336" xr2:uid="{4B54D6C5-B809-4B09-8F2C-D3461C945E11}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B54D6C5-B809-4B09-8F2C-D3461C945E11}"/>
   </bookViews>
   <sheets>
     <sheet name="Entities" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="341">
   <si>
     <t>Key</t>
     <phoneticPr fontId="1"/>
@@ -560,348 +560,618 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>＃貨物船</t>
+    <t>Plain</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バニラ星雲</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワームホール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マイレージ会員</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワープドライブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チョコレートモノリス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジェネレーションシップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダイソン球</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後のフロンティア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自動操縦</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇宙の果てのレストラン</t>
+  </si>
+  <si>
+    <t>共通言語</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トロイド宇宙</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最優先指令</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宇宙前景放射</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30分以内にお届けできなければ全額返金いたします</t>
+  </si>
+  <si>
+    <t>古代の石版</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イカれた麦百姓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>魂と売る契約</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正気のダンス</t>
+  </si>
+  <si>
+    <t>「健全な」踊り</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブレーン移植</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終末に向けた代替案</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>イライラする呪文</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現実世界</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異次元ゴミ投棄場</t>
+  </si>
+  <si>
+    <t>埋め込み式極小ポータル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>彼の降臨</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家庭内分裂</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポータルガン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>帰り道</t>
+  </si>
+  <si>
+    <t>次元転移装置</t>
+  </si>
+  <si>
+    <t>タイムパラドックスリゾルバー</t>
+  </si>
+  <si>
+    <t>量子的難問</t>
+  </si>
+  <si>
+    <t>因果律強制者</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過去と未来の比較</t>
+  </si>
+  <si>
+    <t>遠い未来の法律</t>
+  </si>
+  <si>
+    <t>グレートループ仮説</t>
+  </si>
+  <si>
+    <t>クッキートピアンの夢想</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第二の秒</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加の時計の針</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追憶</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分裂した秒</t>
+  </si>
+  <si>
+    <t>忍耐廃止</t>
+  </si>
+  <si>
+    <t>耐時間性の椅子カバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>過ちを正しに</t>
+  </si>
+  <si>
+    <t>シュガー粒子</t>
+  </si>
+  <si>
+    <t>弦理論</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大型マカロン衝突器</t>
+  </si>
+  <si>
+    <t>ビッグバンベイク</t>
+  </si>
+  <si>
+    <t>リバースサイクロトロン</t>
+  </si>
+  <si>
+    <t>ナノ宇宙学</t>
+  </si>
+  <si>
+    <t>パルス</t>
+  </si>
+  <si>
+    <t>他にも基本的な超微粒子があるだろう、多分</t>
+  </si>
+  <si>
+    <t>量子櫛</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベーキングノーベル賞</t>
+  </si>
+  <si>
+    <t>確定分子</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風味そのもの</t>
+  </si>
+  <si>
+    <t>おいしい引力</t>
+  </si>
+  <si>
+    <t>従業員の小型化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原子の砂糖漬け</t>
+  </si>
+  <si>
+    <t>宝石磨き</t>
+  </si>
+  <si>
+    <t>超純粋宇宙光</t>
+  </si>
+  <si>
+    <t>夜光性</t>
+  </si>
+  <si>
+    <t>陰影反転</t>
+  </si>
+  <si>
+    <t>クリスタルの鏡</t>
+  </si>
+  <si>
+    <t>光速制限</t>
+  </si>
+  <si>
+    <t>オッカムのレーザー</t>
+  </si>
+  <si>
+    <t>ハイパーブラック塗料</t>
+  </si>
+  <si>
+    <t>実験ゴーグル、ただしオシャレカラー</t>
+  </si>
+  <si>
+    <t>光の調達方法</t>
+  </si>
+  <si>
+    <t>逆光理論</t>
+  </si>
+  <si>
+    <t>光の聖域</t>
+  </si>
+  <si>
+    <t>第９の色</t>
+  </si>
+  <si>
+    <t>チョコレートライト</t>
+  </si>
+  <si>
+    <t>穀物色の虹</t>
+  </si>
+  <si>
+    <t>あなたのラッキークッキー</t>
+  </si>
+  <si>
+    <t>「全てが水の泡になる」魔法のコイン</t>
+  </si>
+  <si>
+    <t>抽選勝利チケット</t>
+  </si>
+  <si>
+    <t>四葉のクローバー畑</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トリックに関する虎の巻</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レプラコーンの村</t>
+  </si>
+  <si>
+    <t>不可能発生装置</t>
+  </si>
+  <si>
+    <t>反迷信学</t>
+  </si>
+  <si>
+    <t>ウサギの足</t>
+  </si>
+  <si>
+    <t>改定確率論</t>
+  </si>
+  <si>
+    <t>0 面サイコロ</t>
+  </si>
+  <si>
+    <t>ちょっとした決定論</t>
+  </si>
+  <si>
+    <t>いい流れ</t>
+  </si>
+  <si>
+    <t>ポジティブの最大化</t>
+  </si>
+  <si>
+    <t>ギャンブラーの誤謬の誤謬</t>
+  </si>
+  <si>
+    <t>メタベーカリー</t>
+  </si>
+  <si>
+    <t>マンデルブラウンシュガー</t>
+  </si>
+  <si>
+    <t>フラクタルなまやかし</t>
+  </si>
+  <si>
+    <t>ネスト化された宇宙論</t>
+  </si>
+  <si>
+    <t>メンガースポンジケーキ</t>
+  </si>
+  <si>
+    <t>特にユーモアのある一頭の牛</t>
+  </si>
+  <si>
+    <t>チョコレートウロボロス</t>
+  </si>
+  <si>
+    <t>ネステッド</t>
+  </si>
+  <si>
+    <t>空間充填繊維</t>
+  </si>
+  <si>
+    <t>終わりのない散文の本</t>
+  </si>
+  <si>
+    <t>全ての集合の集合</t>
+  </si>
+  <si>
+    <t>今回のアップグレード</t>
+  </si>
+  <si>
+    <t>箱</t>
+  </si>
+  <si>
+    <t>マルチスケール・プロファイリング</t>
+  </si>
+  <si>
+    <t>同じであればあるほどに</t>
+  </si>
+  <si>
+    <t>猫でも分かるJavaScriptコンソール</t>
+  </si>
+  <si>
+    <t>64ビット配列</t>
+  </si>
+  <si>
+    <t>スタックオーバーフロー</t>
+  </si>
+  <si>
+    <t>エンタープライズコンパイラー</t>
+  </si>
+  <si>
+    <t>シンタックスシュガー</t>
+  </si>
+  <si>
+    <t>一杯のおいしいコーヒー</t>
+  </si>
+  <si>
+    <t>食べる直前にベーキング</t>
+  </si>
+  <si>
+    <t>クッキー++</t>
+  </si>
+  <si>
+    <t>ソフトウエアアップデート</t>
+  </si>
+  <si>
+    <t>Game.Loop</t>
+  </si>
+  <si>
+    <t>eval()</t>
+  </si>
+  <si>
+    <t>君の一番のファン</t>
+  </si>
+  <si>
+    <t>ハッカーの影</t>
+  </si>
+  <si>
+    <t>PHP捕獲用バット</t>
+  </si>
+  <si>
+    <t>シミュレーション用フェールセーフ</t>
+  </si>
+  <si>
+    <t>明白な宿命</t>
+  </si>
+  <si>
+    <t>要するに多次元的宇宙</t>
+  </si>
+  <si>
+    <t>万物の変換</t>
+  </si>
+  <si>
+    <t>マルチバース工作員</t>
+  </si>
+  <si>
+    <t>脱出計画</t>
+  </si>
+  <si>
+    <t>ゲームデザイン</t>
+  </si>
+  <si>
+    <t>宇宙</t>
+  </si>
+  <si>
+    <t>多元宇宙戦争</t>
+  </si>
+  <si>
+    <t>モバイルポート</t>
+  </si>
+  <si>
+    <t>カプセル化リアリティー</t>
+  </si>
+  <si>
+    <t>外部からのクリック</t>
+  </si>
+  <si>
+    <t>ユニバーサル・アイドリング</t>
+  </si>
+  <si>
+    <t>五番目の壁を破れ</t>
+  </si>
+  <si>
+    <t>反対な世界</t>
+  </si>
+  <si>
+    <t>ローマに通じる他の道</t>
+  </si>
+  <si>
+    <t>ニューラル自我制限</t>
+  </si>
+  <si>
+    <t>従え</t>
+  </si>
+  <si>
+    <t>ひとつまみの非合理性</t>
+  </si>
+  <si>
+    <t>前方と後方の脳半球</t>
+  </si>
+  <si>
+    <t>ニューラルネットワーキング</t>
+  </si>
+  <si>
+    <t>宇宙的ブレインストーム</t>
+  </si>
+  <si>
+    <t>メガ・セラピー</t>
+  </si>
+  <si>
+    <t>シナプス用潤滑剤</t>
+  </si>
+  <si>
+    <t>サイコキネシス</t>
+  </si>
+  <si>
+    <t>脊椎</t>
+  </si>
+  <si>
+    <t>ニューラフォーミング</t>
+  </si>
+  <si>
+    <t>認識論的トリック</t>
+  </si>
+  <si>
+    <t>ありとあらゆる考え</t>
+  </si>
+  <si>
+    <t>夢見る土地</t>
+  </si>
+  <si>
+    <t>知的財産の窃盗</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クローンの大おけ</t>
+  </si>
+  <si>
+    <t>エネルギーたっぷりの栄養</t>
+  </si>
+  <si>
+    <t>スタントダブル</t>
+  </si>
+  <si>
+    <t>クローンリサイクルセンター</t>
+  </si>
+  <si>
+    <t>クローンの放し飼い</t>
+  </si>
+  <si>
+    <t>遺伝子調整</t>
+  </si>
+  <si>
+    <t>多様性の力</t>
+  </si>
+  <si>
+    <t>自分をいたわる</t>
+  </si>
+  <si>
+    <t>ソース管理</t>
+  </si>
+  <si>
+    <t>みんなの固い絆</t>
+  </si>
+  <si>
+    <t>安全強化パトロール</t>
+  </si>
+  <si>
+    <t>クローンの権利</t>
+  </si>
+  <si>
+    <t>大家族</t>
+  </si>
+  <si>
+    <t>身体微調整効率化計画</t>
+  </si>
+  <si>
+    <t>寝る前にクローンたちに物語を読み聞かせなきゃ</t>
+  </si>
+  <si>
+    <t>Shipment</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AlchemyLab</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TimeMachine</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AntimatterCondenser</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Prism</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ChanceMaker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FractalEngine</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JavascriptConsole</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Idleverse</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CortexBaker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>You</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#貨物船</t>
     <rPh sb="1" eb="4">
       <t>カモツセン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Plain</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>バニラ星雲</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ワームホール</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マイレージ会員</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ワープドライブ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チョコレートモノリス</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジェネレーションシップ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダイソン球</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>最後のフロンティア</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>自動操縦</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>宇宙の果てのレストラン</t>
-  </si>
-  <si>
-    <t>共通言語</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>トロイド宇宙</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>最優先指令</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>宇宙前景放射</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>30分以内にお届けできなければ全額返金いたします</t>
-  </si>
-  <si>
-    <t>＃錬金術師</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>古代の石版</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イカれた麦百姓</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>魂と売る契約</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>正気のダンス</t>
-  </si>
-  <si>
-    <t>「健全な」踊り</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ブレーン移植</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>終末に向けた代替案</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イライラする呪文</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現実世界</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>異次元ゴミ投棄場</t>
-  </si>
-  <si>
-    <t>埋め込み式極小ポータル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>彼の降臨</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>家庭内分裂</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ポータルガン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>帰り道</t>
-  </si>
-  <si>
-    <t>＃タイムマシン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>次元転移装置</t>
-  </si>
-  <si>
-    <t>タイムパラドックスリゾルバー</t>
-  </si>
-  <si>
-    <t>量子的難問</t>
-  </si>
-  <si>
-    <t>因果律強制者</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>過去と未来の比較</t>
-  </si>
-  <si>
-    <t>遠い未来の法律</t>
-  </si>
-  <si>
-    <t>グレートループ仮説</t>
-  </si>
-  <si>
-    <t>クッキートピアンの夢想</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>第二の秒</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>追加の時計の針</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>追憶</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>分裂した秒</t>
-  </si>
-  <si>
-    <t>忍耐廃止</t>
-  </si>
-  <si>
-    <t>耐時間性の椅子カバー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>過ちを正しに</t>
-  </si>
-  <si>
-    <t>＃反物質コンデンサー</t>
+    <t>#錬金術師</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#タイムマシン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#反物質コンデンサー</t>
     <rPh sb="1" eb="4">
       <t>ハンブッシツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>シュガー粒子</t>
-  </si>
-  <si>
-    <t>弦理論</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>大型マカロン衝突器</t>
-  </si>
-  <si>
-    <t>ビッグバンベイク</t>
-  </si>
-  <si>
-    <t>リバースサイクロトロン</t>
-  </si>
-  <si>
-    <t>ナノ宇宙学</t>
-  </si>
-  <si>
-    <t>パルス</t>
-  </si>
-  <si>
-    <t>他にも基本的な超微粒子があるだろう、多分</t>
-  </si>
-  <si>
-    <t>量子櫛</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベーキングノーベル賞</t>
-  </si>
-  <si>
-    <t>確定分子</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>風味そのもの</t>
-  </si>
-  <si>
-    <t>おいしい引力</t>
-  </si>
-  <si>
-    <t>従業員の小型化</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>原子の砂糖漬け</t>
-  </si>
-  <si>
-    <t>＃プリズム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>宝石磨き</t>
-  </si>
-  <si>
-    <t>超純粋宇宙光</t>
-  </si>
-  <si>
-    <t>夜光性</t>
-  </si>
-  <si>
-    <t>陰影反転</t>
-  </si>
-  <si>
-    <t>クリスタルの鏡</t>
-  </si>
-  <si>
-    <t>光速制限</t>
-  </si>
-  <si>
-    <t>オッカムのレーザー</t>
-  </si>
-  <si>
-    <t>ハイパーブラック塗料</t>
-  </si>
-  <si>
-    <t>実験ゴーグル、ただしオシャレカラー</t>
-  </si>
-  <si>
-    <t>光の調達方法</t>
-  </si>
-  <si>
-    <t>逆光理論</t>
-  </si>
-  <si>
-    <t>光の聖域</t>
-  </si>
-  <si>
-    <t>第９の色</t>
-  </si>
-  <si>
-    <t>チョコレートライト</t>
-  </si>
-  <si>
-    <t>穀物色の虹</t>
-  </si>
-  <si>
-    <t>＃チャンス‐メーカー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>あなたのラッキークッキー</t>
-  </si>
-  <si>
-    <t>「全てが水の泡になる」魔法のコイン</t>
-  </si>
-  <si>
-    <t>抽選勝利チケット</t>
-  </si>
-  <si>
-    <t>四葉のクローバー畑</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>トリックに関する虎の巻</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>レプラコーンの村</t>
-  </si>
-  <si>
-    <t>不可能発生装置</t>
-  </si>
-  <si>
-    <t>反迷信学</t>
-  </si>
-  <si>
-    <t>ウサギの足</t>
-  </si>
-  <si>
-    <t>改定確率論</t>
-  </si>
-  <si>
-    <t>0 面サイコロ</t>
-  </si>
-  <si>
-    <t>ちょっとした決定論</t>
-  </si>
-  <si>
-    <t>いい流れ</t>
-  </si>
-  <si>
-    <t>ポジティブの最大化</t>
-  </si>
-  <si>
-    <t>ギャンブラーの誤謬の誤謬</t>
-  </si>
-  <si>
-    <t>＃自己無限生成エンジン</t>
+    <t>#プリズム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#チャンス‐メーカー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#自己無限生成エンジン</t>
     <rPh sb="1" eb="3">
       <t>ジコ</t>
     </rPh>
@@ -914,246 +1184,20 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>メタベーカリー</t>
-  </si>
-  <si>
-    <t>マンデルブラウンシュガー</t>
-  </si>
-  <si>
-    <t>フラクタルなまやかし</t>
-  </si>
-  <si>
-    <t>ネスト化された宇宙論</t>
-  </si>
-  <si>
-    <t>メンガースポンジケーキ</t>
-  </si>
-  <si>
-    <t>特にユーモアのある一頭の牛</t>
-  </si>
-  <si>
-    <t>チョコレートウロボロス</t>
-  </si>
-  <si>
-    <t>ネステッド</t>
-  </si>
-  <si>
-    <t>空間充填繊維</t>
-  </si>
-  <si>
-    <t>終わりのない散文の本</t>
-  </si>
-  <si>
-    <t>全ての集合の集合</t>
-  </si>
-  <si>
-    <t>今回のアップグレード</t>
-  </si>
-  <si>
-    <t>箱</t>
-  </si>
-  <si>
-    <t>マルチスケール・プロファイリング</t>
-  </si>
-  <si>
-    <t>同じであればあるほどに</t>
-  </si>
-  <si>
-    <t>＃Javascript console</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>猫でも分かるJavaScriptコンソール</t>
-  </si>
-  <si>
-    <t>64ビット配列</t>
-  </si>
-  <si>
-    <t>スタックオーバーフロー</t>
-  </si>
-  <si>
-    <t>エンタープライズコンパイラー</t>
-  </si>
-  <si>
-    <t>シンタックスシュガー</t>
-  </si>
-  <si>
-    <t>一杯のおいしいコーヒー</t>
-  </si>
-  <si>
-    <t>食べる直前にベーキング</t>
-  </si>
-  <si>
-    <t>クッキー++</t>
-  </si>
-  <si>
-    <t>ソフトウエアアップデート</t>
-  </si>
-  <si>
-    <t>Game.Loop</t>
-  </si>
-  <si>
-    <t>eval()</t>
-  </si>
-  <si>
-    <t>君の一番のファン</t>
-  </si>
-  <si>
-    <t>ハッカーの影</t>
-  </si>
-  <si>
-    <t>PHP捕獲用バット</t>
-  </si>
-  <si>
-    <t>シミュレーション用フェールセーフ</t>
-  </si>
-  <si>
-    <t>＃施設</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>明白な宿命</t>
-  </si>
-  <si>
-    <t>要するに多次元的宇宙</t>
-  </si>
-  <si>
-    <t>万物の変換</t>
-  </si>
-  <si>
-    <t>マルチバース工作員</t>
-  </si>
-  <si>
-    <t>脱出計画</t>
-  </si>
-  <si>
-    <t>ゲームデザイン</t>
-  </si>
-  <si>
-    <t>宇宙</t>
-  </si>
-  <si>
-    <t>多元宇宙戦争</t>
-  </si>
-  <si>
-    <t>モバイルポート</t>
-  </si>
-  <si>
-    <t>カプセル化リアリティー</t>
-  </si>
-  <si>
-    <t>外部からのクリック</t>
-  </si>
-  <si>
-    <t>ユニバーサル・アイドリング</t>
-  </si>
-  <si>
-    <t>五番目の壁を破れ</t>
-  </si>
-  <si>
-    <t>反対な世界</t>
-  </si>
-  <si>
-    <t>ローマに通じる他の道</t>
-  </si>
-  <si>
-    <t>＃Cortex baker</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ニューラル自我制限</t>
-  </si>
-  <si>
-    <t>従え</t>
-  </si>
-  <si>
-    <t>ひとつまみの非合理性</t>
-  </si>
-  <si>
-    <t>前方と後方の脳半球</t>
-  </si>
-  <si>
-    <t>ニューラルネットワーキング</t>
-  </si>
-  <si>
-    <t>宇宙的ブレインストーム</t>
-  </si>
-  <si>
-    <t>メガ・セラピー</t>
-  </si>
-  <si>
-    <t>シナプス用潤滑剤</t>
-  </si>
-  <si>
-    <t>サイコキネシス</t>
-  </si>
-  <si>
-    <t>脊椎</t>
-  </si>
-  <si>
-    <t>ニューラフォーミング</t>
-  </si>
-  <si>
-    <t>認識論的トリック</t>
-  </si>
-  <si>
-    <t>ありとあらゆる考え</t>
-  </si>
-  <si>
-    <t>夢見る土地</t>
-  </si>
-  <si>
-    <t>知的財産の窃盗</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>＃You</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>クローンの大おけ</t>
-  </si>
-  <si>
-    <t>エネルギーたっぷりの栄養</t>
-  </si>
-  <si>
-    <t>スタントダブル</t>
-  </si>
-  <si>
-    <t>クローンリサイクルセンター</t>
-  </si>
-  <si>
-    <t>クローンの放し飼い</t>
-  </si>
-  <si>
-    <t>遺伝子調整</t>
-  </si>
-  <si>
-    <t>多様性の力</t>
-  </si>
-  <si>
-    <t>自分をいたわる</t>
-  </si>
-  <si>
-    <t>ソース管理</t>
-  </si>
-  <si>
-    <t>みんなの固い絆</t>
-  </si>
-  <si>
-    <t>安全強化パトロール</t>
-  </si>
-  <si>
-    <t>クローンの権利</t>
-  </si>
-  <si>
-    <t>大家族</t>
-  </si>
-  <si>
-    <t>身体微調整効率化計画</t>
-  </si>
-  <si>
-    <t>寝る前にクローンたちに物語を読み聞かせなきゃ</t>
+    <t>#Javascript console</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#施設</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#Cortex baker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#You</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1231,68 +1275,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3041,1872 +3024,1872 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>153</v>
+        <v>330</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B130" t="s">
+        <v>153</v>
+      </c>
+      <c r="C130" t="s">
         <v>154</v>
-      </c>
-      <c r="C130" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B131" t="s">
         <v>5</v>
       </c>
       <c r="C131" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B132" t="s">
         <v>6</v>
       </c>
       <c r="C132" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B133" t="s">
         <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B134" t="s">
         <v>8</v>
       </c>
       <c r="C134" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B135" t="s">
         <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B136" t="s">
         <v>10</v>
       </c>
       <c r="C136" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B137" t="s">
         <v>11</v>
       </c>
       <c r="C137" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B138" t="s">
         <v>12</v>
       </c>
       <c r="C138" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B139" t="s">
         <v>13</v>
       </c>
       <c r="C139" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B140" t="s">
         <v>14</v>
       </c>
       <c r="C140" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B141" t="s">
         <v>15</v>
       </c>
       <c r="C141" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B142" t="s">
         <v>16</v>
       </c>
       <c r="C142" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B143" t="s">
         <v>17</v>
       </c>
       <c r="C143" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>95</v>
+        <v>319</v>
       </c>
       <c r="B144" t="s">
         <v>18</v>
       </c>
       <c r="C144" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>170</v>
+        <v>331</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C146" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B147" t="s">
         <v>5</v>
       </c>
       <c r="C147" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B148" t="s">
         <v>6</v>
       </c>
       <c r="C148" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B149" t="s">
         <v>7</v>
       </c>
       <c r="C149" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B150" t="s">
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B151" t="s">
         <v>9</v>
       </c>
       <c r="C151" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B152" t="s">
         <v>10</v>
       </c>
       <c r="C152" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B153" t="s">
         <v>11</v>
       </c>
       <c r="C153" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B154" t="s">
         <v>12</v>
       </c>
       <c r="C154" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B155" t="s">
         <v>13</v>
       </c>
       <c r="C155" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B156" t="s">
         <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B157" t="s">
         <v>15</v>
       </c>
       <c r="C157" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B158" t="s">
         <v>16</v>
       </c>
       <c r="C158" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B159" t="s">
         <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="B160" t="s">
         <v>18</v>
       </c>
       <c r="C160" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>186</v>
+        <v>332</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B162" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C162" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B163" t="s">
         <v>5</v>
       </c>
       <c r="C163" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B164" t="s">
         <v>6</v>
       </c>
       <c r="C164" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B165" t="s">
         <v>7</v>
       </c>
       <c r="C165" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B166" t="s">
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B167" t="s">
         <v>9</v>
       </c>
       <c r="C167" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B168" t="s">
         <v>10</v>
       </c>
       <c r="C168" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B169" t="s">
         <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B170" t="s">
         <v>12</v>
       </c>
       <c r="C170" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B171" t="s">
         <v>13</v>
       </c>
       <c r="C171" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B172" t="s">
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B173" t="s">
         <v>15</v>
       </c>
       <c r="C173" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B174" t="s">
         <v>16</v>
       </c>
       <c r="C174" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B175" t="s">
         <v>17</v>
       </c>
       <c r="C175" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="B176" t="s">
         <v>18</v>
       </c>
       <c r="C176" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>202</v>
+        <v>333</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B178" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C178" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B179" t="s">
         <v>5</v>
       </c>
       <c r="C179" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B180" t="s">
         <v>6</v>
       </c>
       <c r="C180" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B181" t="s">
         <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B182" t="s">
         <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B183" t="s">
         <v>9</v>
       </c>
       <c r="C183" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B184" t="s">
         <v>10</v>
       </c>
       <c r="C184" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B185" t="s">
         <v>11</v>
       </c>
       <c r="C185" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B186" t="s">
         <v>12</v>
       </c>
       <c r="C186" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B187" t="s">
         <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B188" t="s">
         <v>14</v>
       </c>
       <c r="C188" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B189" t="s">
         <v>15</v>
       </c>
       <c r="C189" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B190" t="s">
         <v>16</v>
       </c>
       <c r="C190" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B191" t="s">
         <v>17</v>
       </c>
       <c r="C191" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="B192" t="s">
         <v>18</v>
       </c>
       <c r="C192" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>218</v>
+        <v>334</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B194" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C194" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B195" t="s">
         <v>5</v>
       </c>
       <c r="C195" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B196" t="s">
         <v>6</v>
       </c>
       <c r="C196" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B197" t="s">
         <v>7</v>
       </c>
       <c r="C197" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B198" t="s">
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B199" t="s">
         <v>9</v>
       </c>
       <c r="C199" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B200" t="s">
         <v>10</v>
       </c>
       <c r="C200" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B201" t="s">
         <v>11</v>
       </c>
       <c r="C201" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B202" t="s">
         <v>12</v>
       </c>
       <c r="C202" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B203" t="s">
         <v>13</v>
       </c>
       <c r="C203" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B204" t="s">
         <v>14</v>
       </c>
       <c r="C204" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B205" t="s">
         <v>15</v>
       </c>
       <c r="C205" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B206" t="s">
         <v>16</v>
       </c>
       <c r="C206" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B207" t="s">
         <v>17</v>
       </c>
       <c r="C207" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>95</v>
+        <v>323</v>
       </c>
       <c r="B208" t="s">
         <v>18</v>
       </c>
       <c r="C208" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>234</v>
+        <v>335</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B210" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C210" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B211" t="s">
         <v>5</v>
       </c>
       <c r="C211" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B212" t="s">
         <v>6</v>
       </c>
       <c r="C212" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B213" t="s">
         <v>7</v>
       </c>
       <c r="C213" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B214" t="s">
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B215" t="s">
         <v>9</v>
       </c>
       <c r="C215" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B216" t="s">
         <v>10</v>
       </c>
       <c r="C216" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B217" t="s">
         <v>11</v>
       </c>
       <c r="C217" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B218" t="s">
         <v>12</v>
       </c>
       <c r="C218" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B219" t="s">
         <v>13</v>
       </c>
       <c r="C219" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B220" t="s">
         <v>14</v>
       </c>
       <c r="C220" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B221" t="s">
         <v>15</v>
       </c>
       <c r="C221" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B222" t="s">
         <v>16</v>
       </c>
       <c r="C222" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B223" t="s">
         <v>17</v>
       </c>
       <c r="C223" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
-        <v>95</v>
+        <v>324</v>
       </c>
       <c r="B224" t="s">
         <v>18</v>
       </c>
       <c r="C224" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>250</v>
+        <v>336</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B226" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C226" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B227" t="s">
         <v>5</v>
       </c>
       <c r="C227" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B228" t="s">
         <v>6</v>
       </c>
       <c r="C228" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B229" t="s">
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B230" t="s">
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B231" t="s">
         <v>9</v>
       </c>
       <c r="C231" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B232" t="s">
         <v>10</v>
       </c>
       <c r="C232" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B233" t="s">
         <v>11</v>
       </c>
       <c r="C233" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B234" t="s">
         <v>12</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B235" t="s">
         <v>13</v>
       </c>
       <c r="C235" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B236" t="s">
         <v>14</v>
       </c>
       <c r="C236" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B237" t="s">
         <v>15</v>
       </c>
       <c r="C237" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B238" t="s">
         <v>16</v>
       </c>
       <c r="C238" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B239" t="s">
         <v>17</v>
       </c>
       <c r="C239" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="B240" t="s">
         <v>18</v>
       </c>
       <c r="C240" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B242" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C242" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B243" t="s">
         <v>5</v>
       </c>
       <c r="C243" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B244" t="s">
         <v>6</v>
       </c>
       <c r="C244" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B245" t="s">
         <v>7</v>
       </c>
       <c r="C245" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B246" t="s">
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B247" t="s">
         <v>9</v>
       </c>
       <c r="C247" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B248" t="s">
         <v>10</v>
       </c>
       <c r="C248" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B249" t="s">
         <v>11</v>
       </c>
       <c r="C249" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B250" t="s">
         <v>12</v>
       </c>
       <c r="C250" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B251" t="s">
         <v>13</v>
       </c>
       <c r="C251" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B252" t="s">
         <v>14</v>
       </c>
       <c r="C252" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B253" t="s">
         <v>15</v>
       </c>
       <c r="C253" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B254" t="s">
         <v>16</v>
       </c>
       <c r="C254" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B255" t="s">
         <v>17</v>
       </c>
       <c r="C255" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
-        <v>95</v>
+        <v>326</v>
       </c>
       <c r="B256" t="s">
         <v>18</v>
       </c>
       <c r="C256" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
-        <v>282</v>
+        <v>338</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B258" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C258" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B259" t="s">
         <v>5</v>
       </c>
       <c r="C259" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B260" t="s">
         <v>6</v>
       </c>
       <c r="C260" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B261" t="s">
         <v>7</v>
       </c>
       <c r="C261" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B262" t="s">
         <v>8</v>
       </c>
       <c r="C262" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B263" t="s">
         <v>9</v>
       </c>
       <c r="C263" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B264" t="s">
         <v>10</v>
       </c>
       <c r="C264" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B265" t="s">
         <v>11</v>
       </c>
       <c r="C265" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B266" t="s">
         <v>12</v>
       </c>
       <c r="C266" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B267" t="s">
         <v>13</v>
       </c>
       <c r="C267" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B268" t="s">
         <v>14</v>
       </c>
       <c r="C268" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B269" t="s">
         <v>15</v>
       </c>
       <c r="C269" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B270" t="s">
         <v>16</v>
       </c>
       <c r="C270" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B271" t="s">
         <v>17</v>
       </c>
       <c r="C271" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="B272" t="s">
         <v>18</v>
       </c>
       <c r="C272" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
-        <v>298</v>
+        <v>339</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B274" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C274" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B275" t="s">
         <v>5</v>
       </c>
       <c r="C275" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B276" t="s">
         <v>6</v>
       </c>
       <c r="C276" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B277" t="s">
         <v>7</v>
       </c>
       <c r="C277" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B278" t="s">
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B279" t="s">
         <v>9</v>
       </c>
       <c r="C279" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B280" t="s">
         <v>10</v>
       </c>
       <c r="C280" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B281" t="s">
         <v>11</v>
       </c>
       <c r="C281" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B282" t="s">
         <v>12</v>
       </c>
       <c r="C282" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B283" t="s">
         <v>13</v>
       </c>
       <c r="C283" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B284" t="s">
         <v>14</v>
       </c>
       <c r="C284" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B285" t="s">
         <v>15</v>
       </c>
       <c r="C285" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B286" t="s">
         <v>16</v>
       </c>
       <c r="C286" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B287" t="s">
         <v>17</v>
       </c>
       <c r="C287" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
-        <v>95</v>
+        <v>328</v>
       </c>
       <c r="B288" t="s">
         <v>18</v>
       </c>
       <c r="C288" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B290" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C290" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B291" t="s">
         <v>5</v>
       </c>
       <c r="C291" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B292" t="s">
         <v>6</v>
       </c>
       <c r="C292" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B293" t="s">
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B294" t="s">
         <v>8</v>
       </c>
       <c r="C294" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B295" t="s">
         <v>9</v>
       </c>
       <c r="C295" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B296" t="s">
         <v>10</v>
       </c>
       <c r="C296" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B297" t="s">
         <v>11</v>
       </c>
       <c r="C297" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B298" t="s">
         <v>12</v>
       </c>
       <c r="C298" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B299" t="s">
         <v>13</v>
       </c>
       <c r="C299" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B300" t="s">
         <v>14</v>
       </c>
       <c r="C300" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B301" t="s">
         <v>15</v>
       </c>
       <c r="C301" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B302" t="s">
         <v>16</v>
       </c>
       <c r="C302" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B303" t="s">
         <v>17</v>
       </c>
       <c r="C303" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="B304" t="s">
         <v>18</v>
       </c>
       <c r="C304" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/Upgrades/Upgrades.xlsx
+++ b/Assets/Excel/Upgrades/Upgrades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PS23B\Unity\VGATeamD\Assets\Excel\Upgrades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8040BF4D-4003-4F9F-B0C4-BDEA5FA60EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D89193-2B35-43CF-9547-2329E45331DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4B54D6C5-B809-4B09-8F2C-D3461C945E11}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="358">
   <si>
     <t>Key</t>
     <phoneticPr fontId="1"/>
@@ -622,10 +622,6 @@
     <t>30分以内にお届けできなければ全額返金いたします</t>
   </si>
   <si>
-    <t>古代の石版</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>イカれた麦百姓</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -637,30 +633,7 @@
     <t>正気のダンス</t>
   </si>
   <si>
-    <t>「健全な」踊り</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ブレーン移植</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>終末に向けた代替案</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>イライラする呪文</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>現実世界</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>異次元ゴミ投棄場</t>
-  </si>
-  <si>
-    <t>埋め込み式極小ポータル</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1145,10 +1118,6 @@
     <rPh sb="1" eb="4">
       <t>カモツセン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>#錬金術師</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1198,6 +1167,85 @@
   <si>
     <t>#You</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#ポータル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Portal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>古代の石版</t>
+  </si>
+  <si>
+    <t>ブレーン移植</t>
+  </si>
+  <si>
+    <t>神サイズのポータル</t>
+  </si>
+  <si>
+    <t>イライラする呪文</t>
+  </si>
+  <si>
+    <t>現実世界</t>
+  </si>
+  <si>
+    <t>次元ゴミ回収機</t>
+  </si>
+  <si>
+    <t>埋め込まれたマイクロポータル</t>
+  </si>
+  <si>
+    <t>#錬金術ラボ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンチモン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生地のエッセンス</t>
+  </si>
+  <si>
+    <t>正真正銘のチョコレート</t>
+  </si>
+  <si>
+    <t>神々の食べ物</t>
+  </si>
+  <si>
+    <t>クラスト硬化液</t>
+  </si>
+  <si>
+    <t>起源のるつぼ</t>
+  </si>
+  <si>
+    <t>原子流動性論</t>
+  </si>
+  <si>
+    <t>ベージュ・グー</t>
+  </si>
+  <si>
+    <t>化学の出現</t>
+  </si>
+  <si>
+    <t>再考した結果</t>
+  </si>
+  <si>
+    <t>公衆の向上</t>
+  </si>
+  <si>
+    <t>錬金術の和解</t>
+  </si>
+  <si>
+    <t>色彩循環</t>
+  </si>
+  <si>
+    <t>神秘のガラス製品</t>
+  </si>
+  <si>
+    <t>毒の一服</t>
   </si>
 </sst>
 </file>
@@ -1585,7 +1633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222065CF-7C40-4549-836B-B81F737954AC}">
-  <dimension ref="A1:D304"/>
+  <dimension ref="A1:D320"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.69921875" customWidth="1"/>
@@ -3024,12 +3072,12 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B130" t="s">
         <v>153</v>
@@ -3040,7 +3088,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B131" t="s">
         <v>5</v>
@@ -3051,7 +3099,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B132" t="s">
         <v>6</v>
@@ -3062,7 +3110,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B133" t="s">
         <v>7</v>
@@ -3073,7 +3121,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B134" t="s">
         <v>8</v>
@@ -3084,7 +3132,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B135" t="s">
         <v>9</v>
@@ -3095,7 +3143,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B136" t="s">
         <v>10</v>
@@ -3106,7 +3154,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B137" t="s">
         <v>11</v>
@@ -3117,7 +3165,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B138" t="s">
         <v>12</v>
@@ -3128,7 +3176,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B139" t="s">
         <v>13</v>
@@ -3139,7 +3187,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B140" t="s">
         <v>14</v>
@@ -3150,7 +3198,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B141" t="s">
         <v>15</v>
@@ -3161,7 +3209,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B142" t="s">
         <v>16</v>
@@ -3172,7 +3220,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B143" t="s">
         <v>17</v>
@@ -3183,7 +3231,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="B144" t="s">
         <v>18</v>
@@ -3194,1702 +3242,1872 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B146" t="s">
         <v>153</v>
       </c>
       <c r="C146" t="s">
-        <v>169</v>
+        <v>343</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B147" t="s">
         <v>5</v>
       </c>
       <c r="C147" t="s">
-        <v>170</v>
+        <v>344</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B148" t="s">
         <v>6</v>
       </c>
       <c r="C148" t="s">
-        <v>171</v>
+        <v>345</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B149" t="s">
         <v>7</v>
       </c>
       <c r="C149" t="s">
-        <v>173</v>
+        <v>346</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B150" t="s">
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>172</v>
+        <v>347</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B151" t="s">
         <v>9</v>
       </c>
       <c r="C151" t="s">
-        <v>174</v>
+        <v>348</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B152" t="s">
         <v>10</v>
       </c>
       <c r="C152" t="s">
-        <v>175</v>
+        <v>349</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B153" t="s">
         <v>11</v>
       </c>
       <c r="C153" t="s">
-        <v>176</v>
+        <v>350</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B154" t="s">
         <v>12</v>
       </c>
       <c r="C154" t="s">
-        <v>177</v>
+        <v>351</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B155" t="s">
         <v>13</v>
       </c>
       <c r="C155" t="s">
-        <v>178</v>
+        <v>352</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B156" t="s">
         <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>179</v>
+        <v>353</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B157" t="s">
         <v>15</v>
       </c>
       <c r="C157" t="s">
-        <v>180</v>
+        <v>354</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B158" t="s">
         <v>16</v>
       </c>
       <c r="C158" t="s">
-        <v>181</v>
+        <v>355</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B159" t="s">
         <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>182</v>
+        <v>356</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B160" t="s">
         <v>18</v>
       </c>
       <c r="C160" t="s">
-        <v>183</v>
+        <v>357</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B162" t="s">
         <v>153</v>
       </c>
       <c r="C162" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B163" t="s">
         <v>5</v>
       </c>
       <c r="C163" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B164" t="s">
         <v>6</v>
       </c>
       <c r="C164" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B165" t="s">
         <v>7</v>
       </c>
       <c r="C165" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B166" t="s">
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B167" t="s">
         <v>9</v>
       </c>
       <c r="C167" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B168" t="s">
         <v>10</v>
       </c>
       <c r="C168" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B169" t="s">
         <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B170" t="s">
         <v>12</v>
       </c>
       <c r="C170" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B171" t="s">
         <v>13</v>
       </c>
       <c r="C171" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B172" t="s">
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B173" t="s">
         <v>15</v>
       </c>
       <c r="C173" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B174" t="s">
         <v>16</v>
       </c>
       <c r="C174" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B175" t="s">
         <v>17</v>
       </c>
       <c r="C175" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B176" t="s">
         <v>18</v>
       </c>
       <c r="C176" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B178" t="s">
         <v>153</v>
       </c>
       <c r="C178" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B179" t="s">
         <v>5</v>
       </c>
       <c r="C179" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B180" t="s">
         <v>6</v>
       </c>
       <c r="C180" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B181" t="s">
         <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B182" t="s">
         <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B183" t="s">
         <v>9</v>
       </c>
       <c r="C183" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B184" t="s">
         <v>10</v>
       </c>
       <c r="C184" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B185" t="s">
         <v>11</v>
       </c>
       <c r="C185" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B186" t="s">
         <v>12</v>
       </c>
       <c r="C186" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B187" t="s">
         <v>13</v>
       </c>
       <c r="C187" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B188" t="s">
         <v>14</v>
       </c>
       <c r="C188" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B189" t="s">
         <v>15</v>
       </c>
       <c r="C189" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B190" t="s">
         <v>16</v>
       </c>
       <c r="C190" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B191" t="s">
         <v>17</v>
       </c>
       <c r="C191" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B192" t="s">
         <v>18</v>
       </c>
       <c r="C192" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B194" t="s">
         <v>153</v>
       </c>
       <c r="C194" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B195" t="s">
         <v>5</v>
       </c>
       <c r="C195" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B196" t="s">
         <v>6</v>
       </c>
       <c r="C196" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B197" t="s">
         <v>7</v>
       </c>
       <c r="C197" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B198" t="s">
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B199" t="s">
         <v>9</v>
       </c>
       <c r="C199" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B200" t="s">
         <v>10</v>
       </c>
       <c r="C200" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B201" t="s">
         <v>11</v>
       </c>
       <c r="C201" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B202" t="s">
         <v>12</v>
       </c>
       <c r="C202" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B203" t="s">
         <v>13</v>
       </c>
       <c r="C203" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B204" t="s">
         <v>14</v>
       </c>
       <c r="C204" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B205" t="s">
         <v>15</v>
       </c>
       <c r="C205" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B206" t="s">
         <v>16</v>
       </c>
       <c r="C206" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B207" t="s">
         <v>17</v>
       </c>
       <c r="C207" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B208" t="s">
         <v>18</v>
       </c>
       <c r="C208" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B210" t="s">
         <v>153</v>
       </c>
       <c r="C210" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B211" t="s">
         <v>5</v>
       </c>
       <c r="C211" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B212" t="s">
         <v>6</v>
       </c>
       <c r="C212" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B213" t="s">
         <v>7</v>
       </c>
       <c r="C213" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B214" t="s">
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B215" t="s">
         <v>9</v>
       </c>
       <c r="C215" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B216" t="s">
         <v>10</v>
       </c>
       <c r="C216" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B217" t="s">
         <v>11</v>
       </c>
       <c r="C217" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B218" t="s">
         <v>12</v>
       </c>
       <c r="C218" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B219" t="s">
         <v>13</v>
       </c>
       <c r="C219" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B220" t="s">
         <v>14</v>
       </c>
       <c r="C220" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B221" t="s">
         <v>15</v>
       </c>
       <c r="C221" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B222" t="s">
         <v>16</v>
       </c>
       <c r="C222" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B223" t="s">
         <v>17</v>
       </c>
       <c r="C223" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B224" t="s">
         <v>18</v>
       </c>
       <c r="C224" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B226" t="s">
         <v>153</v>
       </c>
       <c r="C226" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B227" t="s">
         <v>5</v>
       </c>
       <c r="C227" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B228" t="s">
         <v>6</v>
       </c>
       <c r="C228" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B229" t="s">
         <v>7</v>
       </c>
       <c r="C229" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B230" t="s">
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B231" t="s">
         <v>9</v>
       </c>
       <c r="C231" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B232" t="s">
         <v>10</v>
       </c>
       <c r="C232" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B233" t="s">
         <v>11</v>
       </c>
       <c r="C233" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B234" t="s">
         <v>12</v>
       </c>
       <c r="C234" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B235" t="s">
         <v>13</v>
       </c>
       <c r="C235" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B236" t="s">
         <v>14</v>
       </c>
       <c r="C236" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B237" t="s">
         <v>15</v>
       </c>
       <c r="C237" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B238" t="s">
         <v>16</v>
       </c>
       <c r="C238" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B239" t="s">
         <v>17</v>
       </c>
       <c r="C239" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B240" t="s">
         <v>18</v>
       </c>
       <c r="C240" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B242" t="s">
         <v>153</v>
       </c>
       <c r="C242" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B243" t="s">
         <v>5</v>
       </c>
       <c r="C243" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B244" t="s">
         <v>6</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B245" t="s">
         <v>7</v>
       </c>
       <c r="C245" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B246" t="s">
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B247" t="s">
         <v>9</v>
       </c>
       <c r="C247" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B248" t="s">
         <v>10</v>
       </c>
       <c r="C248" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B249" t="s">
         <v>11</v>
       </c>
       <c r="C249" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B250" t="s">
         <v>12</v>
       </c>
       <c r="C250" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B251" t="s">
         <v>13</v>
       </c>
       <c r="C251" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B252" t="s">
         <v>14</v>
       </c>
       <c r="C252" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B253" t="s">
         <v>15</v>
       </c>
       <c r="C253" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B254" t="s">
         <v>16</v>
       </c>
       <c r="C254" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B255" t="s">
         <v>17</v>
       </c>
       <c r="C255" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B256" t="s">
         <v>18</v>
       </c>
       <c r="C256" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B258" t="s">
         <v>153</v>
       </c>
       <c r="C258" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B259" t="s">
         <v>5</v>
       </c>
       <c r="C259" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B260" t="s">
         <v>6</v>
       </c>
       <c r="C260" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B261" t="s">
         <v>7</v>
       </c>
       <c r="C261" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B262" t="s">
         <v>8</v>
       </c>
       <c r="C262" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B263" t="s">
         <v>9</v>
       </c>
       <c r="C263" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B264" t="s">
         <v>10</v>
       </c>
       <c r="C264" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B265" t="s">
         <v>11</v>
       </c>
       <c r="C265" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B266" t="s">
         <v>12</v>
       </c>
       <c r="C266" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B267" t="s">
         <v>13</v>
       </c>
       <c r="C267" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B268" t="s">
         <v>14</v>
       </c>
       <c r="C268" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B269" t="s">
         <v>15</v>
       </c>
       <c r="C269" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B270" t="s">
         <v>16</v>
       </c>
       <c r="C270" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B271" t="s">
         <v>17</v>
       </c>
       <c r="C271" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B272" t="s">
         <v>18</v>
       </c>
       <c r="C272" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B274" t="s">
         <v>153</v>
       </c>
       <c r="C274" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B275" t="s">
         <v>5</v>
       </c>
       <c r="C275" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B276" t="s">
         <v>6</v>
       </c>
       <c r="C276" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B277" t="s">
         <v>7</v>
       </c>
       <c r="C277" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B278" t="s">
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B279" t="s">
         <v>9</v>
       </c>
       <c r="C279" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B280" t="s">
         <v>10</v>
       </c>
       <c r="C280" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B281" t="s">
         <v>11</v>
       </c>
       <c r="C281" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B282" t="s">
         <v>12</v>
       </c>
       <c r="C282" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B283" t="s">
         <v>13</v>
       </c>
       <c r="C283" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B284" t="s">
         <v>14</v>
       </c>
       <c r="C284" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B285" t="s">
         <v>15</v>
       </c>
       <c r="C285" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B286" t="s">
         <v>16</v>
       </c>
       <c r="C286" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B287" t="s">
         <v>17</v>
       </c>
       <c r="C287" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B288" t="s">
         <v>18</v>
       </c>
       <c r="C288" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B290" t="s">
         <v>153</v>
       </c>
       <c r="C290" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B291" t="s">
         <v>5</v>
       </c>
       <c r="C291" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B292" t="s">
         <v>6</v>
       </c>
       <c r="C292" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B293" t="s">
         <v>7</v>
       </c>
       <c r="C293" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B294" t="s">
         <v>8</v>
       </c>
       <c r="C294" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B295" t="s">
         <v>9</v>
       </c>
       <c r="C295" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B296" t="s">
         <v>10</v>
       </c>
       <c r="C296" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B297" t="s">
         <v>11</v>
       </c>
       <c r="C297" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B298" t="s">
         <v>12</v>
       </c>
       <c r="C298" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B299" t="s">
         <v>13</v>
       </c>
       <c r="C299" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B300" t="s">
         <v>14</v>
       </c>
       <c r="C300" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B301" t="s">
         <v>15</v>
       </c>
       <c r="C301" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B302" t="s">
         <v>16</v>
       </c>
       <c r="C302" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B303" t="s">
         <v>17</v>
       </c>
       <c r="C303" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B304" t="s">
         <v>18</v>
       </c>
       <c r="C304" t="s">
-        <v>318</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A305" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A306" t="s">
+        <v>334</v>
+      </c>
+      <c r="B306" t="s">
+        <v>153</v>
+      </c>
+      <c r="C306" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A307" t="s">
+        <v>334</v>
+      </c>
+      <c r="B307" t="s">
+        <v>5</v>
+      </c>
+      <c r="C307" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A308" t="s">
+        <v>334</v>
+      </c>
+      <c r="B308" t="s">
+        <v>6</v>
+      </c>
+      <c r="C308" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A309" t="s">
+        <v>334</v>
+      </c>
+      <c r="B309" t="s">
+        <v>7</v>
+      </c>
+      <c r="C309" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A310" t="s">
+        <v>334</v>
+      </c>
+      <c r="B310" t="s">
+        <v>8</v>
+      </c>
+      <c r="C310" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A311" t="s">
+        <v>334</v>
+      </c>
+      <c r="B311" t="s">
+        <v>9</v>
+      </c>
+      <c r="C311" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A312" t="s">
+        <v>334</v>
+      </c>
+      <c r="B312" t="s">
+        <v>10</v>
+      </c>
+      <c r="C312" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A313" t="s">
+        <v>334</v>
+      </c>
+      <c r="B313" t="s">
+        <v>11</v>
+      </c>
+      <c r="C313" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A314" t="s">
+        <v>334</v>
+      </c>
+      <c r="B314" t="s">
+        <v>12</v>
+      </c>
+      <c r="C314" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A315" t="s">
+        <v>334</v>
+      </c>
+      <c r="B315" t="s">
+        <v>13</v>
+      </c>
+      <c r="C315" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A316" t="s">
+        <v>334</v>
+      </c>
+      <c r="B316" t="s">
+        <v>14</v>
+      </c>
+      <c r="C316" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A317" t="s">
+        <v>334</v>
+      </c>
+      <c r="B317" t="s">
+        <v>15</v>
+      </c>
+      <c r="C317" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A318" t="s">
+        <v>334</v>
+      </c>
+      <c r="B318" t="s">
+        <v>16</v>
+      </c>
+      <c r="C318" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A319" t="s">
+        <v>334</v>
+      </c>
+      <c r="B319" t="s">
+        <v>17</v>
+      </c>
+      <c r="C319" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A320" t="s">
+        <v>334</v>
+      </c>
+      <c r="B320" t="s">
+        <v>18</v>
+      </c>
+      <c r="C320" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
